--- a/public/templates/REG-010_v6 Charla Inicial.xlsx
+++ b/public/templates/REG-010_v6 Charla Inicial.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chico\OneDrive\Documents\Rayca\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chico\OneDrive\Documents\GitHub\FillAndSend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FDE8C0-8225-44E7-B4E7-35C556ED3E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C362FF4-70E8-4B53-B1A9-BDF8F2EEEB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8EF73867-AC56-4CD5-A280-234971FB6F14}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
   <si>
     <t>Versión: 06</t>
   </si>
@@ -285,7 +285,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -378,116 +378,178 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -865,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9668F1-F994-4ED1-8E8B-D0B82210C176}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
@@ -873,535 +935,575 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13" t="s">
+      <c r="A1" s="31"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="17" t="s">
+      <c r="D1" s="32"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="17" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="17" t="s">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="38"/>
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="18" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="18"/>
+      <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="30"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="30"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="25" t="s">
+      <c r="A12" s="5"/>
+      <c r="B12" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
-      <c r="B13" s="25" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23" t="s">
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="25" t="s">
+      <c r="A14" s="5"/>
+      <c r="B14" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="25" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="22"/>
-      <c r="B16" s="25" t="s">
+      <c r="A16" s="5"/>
+      <c r="B16" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="23" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="5"/>
+      <c r="B17" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="23" t="s">
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="25" t="s">
+      <c r="A18" s="5"/>
+      <c r="B18" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23" t="s">
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="22"/>
-      <c r="B19" s="25" t="s">
+      <c r="A19" s="5"/>
+      <c r="B19" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30" t="s">
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="30" t="s">
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="4" t="s">
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="33"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="4" t="s">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="34"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="4" t="s">
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="34"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="4" t="s">
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="34"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="4" t="s">
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="34"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="4" t="s">
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="34"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="4" t="s">
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="34"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="4" t="s">
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="34"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="4" t="s">
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="34"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="5" t="s">
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="22"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="5" t="s">
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="22"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
+      <c r="A34" s="45"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="30"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="30"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="13"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="37"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
+      <c r="A40" s="14"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="24" t="s">
+      <c r="A41" s="14"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="16"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="E31:G31"/>
+  <mergeCells count="62">
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="E32:G32"/>
     <mergeCell ref="A33:H33"/>
@@ -1430,6 +1532,10 @@
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="E31:G31"/>
     <mergeCell ref="D5:H5"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="C1:E3"/>
@@ -1444,22 +1550,22 @@
     <mergeCell ref="A8:H10"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="F12:H12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="F12:H12"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="F17:H17"/>
-    <mergeCell ref="A38:E41"/>
-    <mergeCell ref="F38:H40"/>
-    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E42:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="A38:H41"/>
+    <mergeCell ref="A42:D44"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
